--- a/data/trans_bre/P5_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 14,78</t>
+          <t>-16,5; 14,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 13,15</t>
+          <t>-15,95; 14,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 7,89</t>
+          <t>-24,53; 6,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 3,79</t>
+          <t>-23,41; 2,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 42,81</t>
+          <t>-32,4; 43,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 47,72</t>
+          <t>-37,19; 54,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 29,15</t>
+          <t>-51,39; 20,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-73,47; 25,26</t>
+          <t>-74,14; 14,9</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 4,26</t>
+          <t>-6,14; 4,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 7,13</t>
+          <t>-6,09; 6,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 4,9</t>
+          <t>-6,74; 4,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 21,35</t>
+          <t>0,31; 23,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 17,53</t>
+          <t>-20,88; 20,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 20,85</t>
+          <t>-14,9; 20,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 15,38</t>
+          <t>-18,46; 13,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 156,97</t>
+          <t>1,04; 150,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 10,5</t>
+          <t>-6,96; 10,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 7,69</t>
+          <t>-11,51; 9,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 5,72</t>
+          <t>-14,26; 5,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 8,47</t>
+          <t>-6,34; 9,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 49,69</t>
+          <t>-24,06; 49,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 20,87</t>
+          <t>-24,51; 25,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 14,44</t>
+          <t>-30,04; 14,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 55,99</t>
+          <t>-27,07; 63,86</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 4,42</t>
+          <t>-4,46; 4,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,99</t>
+          <t>-5,31; 4,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,74</t>
+          <t>-6,96; 2,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 15,42</t>
+          <t>-0,52; 14,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 17,42</t>
+          <t>-14,53; 17,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 14,08</t>
+          <t>-12,94; 13,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 7,8</t>
+          <t>-17,8; 6,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 94,72</t>
+          <t>-3,43; 93,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 14,26</t>
+          <t>-16,82; 14,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 14,64</t>
+          <t>-16,4; 13,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,53; 6,48</t>
+          <t>-26,11; 5,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 2,34</t>
+          <t>-23,49; 2,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 43,4</t>
+          <t>-34,04; 44,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 54,56</t>
+          <t>-38,94; 42,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 20,45</t>
+          <t>-53,75; 17,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,14; 14,9</t>
+          <t>-74,19; 23,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 4,91</t>
+          <t>-6,09; 5,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 6,83</t>
+          <t>-5,18; 7,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 4,27</t>
+          <t>-6,37; 5,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 23,17</t>
+          <t>0,57; 23,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 20,37</t>
+          <t>-20,61; 22,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 20,18</t>
+          <t>-12,93; 20,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 13,0</t>
+          <t>-17,3; 16,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 150,58</t>
+          <t>3,19; 180,15</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 10,13</t>
+          <t>-7,75; 10,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 9,1</t>
+          <t>-12,72; 8,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 5,27</t>
+          <t>-13,06; 5,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 9,09</t>
+          <t>-5,52; 9,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 49,99</t>
+          <t>-25,63; 50,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 25,49</t>
+          <t>-26,71; 22,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 14,16</t>
+          <t>-28,34; 13,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 63,86</t>
+          <t>-25,37; 64,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,56</t>
+          <t>-4,13; 4,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,87</t>
+          <t>-5,29; 4,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 2,36</t>
+          <t>-7,73; 2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,4</t>
+          <t>-0,59; 14,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 17,81</t>
+          <t>-13,9; 17,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 13,67</t>
+          <t>-12,98; 12,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 6,8</t>
+          <t>-18,99; 6,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 93,96</t>
+          <t>-3,99; 92,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P5_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-10,14</t>
+          <t>-6,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-42,35%</t>
+          <t>-25,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 14,7</t>
+          <t>-16,49; 14,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 13,02</t>
+          <t>-15,65; 13,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 5,66</t>
+          <t>-25,48; 7,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 2,98</t>
+          <t>-20,01; 9,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,04; 44,2</t>
+          <t>-33,83; 42,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,94; 42,37</t>
+          <t>-35,53; 47,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 17,74</t>
+          <t>-53,16; 29,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 23,3</t>
+          <t>-63,56; 61,11</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 5,39</t>
+          <t>-6,16; 4,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 7,12</t>
+          <t>-5,08; 7,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 5,47</t>
+          <t>-6,28; 4,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 23,38</t>
+          <t>-2,47; 6,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 22,54</t>
+          <t>-20,76; 17,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 20,59</t>
+          <t>-12,7; 20,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 16,16</t>
+          <t>-16,37; 15,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 180,15</t>
+          <t>-13,43; 43,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 10,34</t>
+          <t>-6,86; 10,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 8,01</t>
+          <t>-12,46; 7,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 5,07</t>
+          <t>-13,04; 5,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 9,23</t>
+          <t>-6,92; 8,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 50,27</t>
+          <t>-24,07; 49,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 22,6</t>
+          <t>-26,49; 20,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 13,12</t>
+          <t>-27,82; 14,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 64,43</t>
+          <t>-30,11; 55,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,53</t>
+          <t>-4,22; 4,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,48</t>
+          <t>-5,4; 4,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 2,14</t>
+          <t>-7,02; 2,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 14,73</t>
+          <t>-2,68; 4,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 17,33</t>
+          <t>-14,08; 17,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 12,29</t>
+          <t>-12,86; 14,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 6,08</t>
+          <t>-17,94; 7,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 92,1</t>
+          <t>-14,1; 30,7</t>
         </is>
       </c>
     </row>
